--- a/ig/DM-OCTOBRE-2026/ValueSet-jdv-hl7-v3-ActPharmacySupplyType-cisis.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-jdv-hl7-v3-ActPharmacySupplyType-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260916095457</t>
+    <t>20260928134055</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:54:57+01:00</t>
+    <t>2026-09-28T13:40:55+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
